--- a/data/trans_dic/IP31KM03_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM03_2023-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,74; 96,68</t>
+          <t>78,88; 95,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,53; 95,17</t>
+          <t>81,56; 96,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,43; 94,7</t>
+          <t>83,22; 94,24</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,15%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,57; 88,19</t>
+          <t>78,78; 85,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,22; 85,86</t>
+          <t>81,03; 87,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,29; 86,13</t>
+          <t>80,73; 85,33</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75,84; 86,68</t>
+          <t>79,22; 89,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,13; 89,6</t>
+          <t>76,17; 86,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79,86; 87,05</t>
+          <t>80,07; 87,23</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,78%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,93; 87,15</t>
+          <t>80,68; 85,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,89; 86,24</t>
+          <t>81,52; 86,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,39; 85,96</t>
+          <t>81,91; 85,51</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>49235</t>
+          <t>47747</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52233</t>
+          <t>41463</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101467</t>
+          <t>89209</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44431; 51919</t>
+          <t>42371; 51230</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46403; 55526</t>
+          <t>37438; 44068</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94592; 106101</t>
+          <t>82903; 93883</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>526</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>383238</t>
+          <t>383726</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>417329</t>
+          <t>357176</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>800567</t>
+          <t>740903</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>368545; 398491</t>
+          <t>367455; 398424</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>400247; 433821</t>
+          <t>344115; 370041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>777990; 824293</t>
+          <t>719387; 760325</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>182</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>119614</t>
+          <t>142249</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>154493</t>
+          <t>120606</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>274106</t>
+          <t>262855</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>110870; 126710</t>
+          <t>132050; 149514</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>145154; 162297</t>
+          <t>112074; 127770</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>261390; 284947</t>
+          <t>251275; 273751</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>768</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>552087</t>
+          <t>573722</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>624054</t>
+          <t>519245</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1176141</t>
+          <t>1092967</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>533965; 567974</t>
+          <t>554146; 590560</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>602396; 642254</t>
+          <t>503550; 532952</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1150483; 1200338</t>
+          <t>1068520; 1115550</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM03_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM03_2023-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman verduras frescas o cocinadas una vez al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>88,89%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>90,32%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>89,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>78,88; 95,37</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>81,56; 96,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>83,22; 94,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>82,27%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>84,11%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>83,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>78,78; 85,42</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>81,03; 87,14</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>80,73; 85,33</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>85,34%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>81,97%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>79,22; 89,7</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>76,17; 86,84</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>80,07; 87,23</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>83,53%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>80,68; 85,98</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>81,52; 86,28</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81,91; 85,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8888910575019615</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9032268710097205</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8954970166910607</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>47747</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41463</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>89209</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.7888074052642035</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8155514670909776</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8321887468828019</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>42371; 51230</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>37438; 44068</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>82903; 93883</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9537375635248875</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9599920388462631</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9424143317379606</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8227001211522249</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8410757238845105</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8314573772484867</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>383726</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>357176</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>740903</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.7878150698858812</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8103180474997143</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8073112758554055</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>367455; 398424</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>344115; 370041</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>719387; 760325</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.8542122856398678</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.8713691035754854</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.8532531038157478</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.8533959145011711</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.819670178418981</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8375833105602599</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>142249</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>120606</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>262855</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.7922094291687291</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.7616859687809897</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.800685970292539</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>132050; 149514</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>112074; 127770</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>251275; 273751</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8969779359490049</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.8683587004628894</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8723054072806512</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>784</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1552</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8353263234292188</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.8405956112436216</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8378213869039779</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>573722</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>519245</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1092967</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8068234038599538</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8151865733231485</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8190809844938796</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>554146; 590560</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>503550; 532952</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1068520; 1115550</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.8598411009676892</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8627861540782178</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8551320109980158</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman verduras frescas o cocinadas una vez al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>47747</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>41463</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>89209</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>42371</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>37438</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>82903</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>51230</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>44068</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>93883</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>517</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>526</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>383726</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>357176</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>740903</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>367455</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>344115</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>719387</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>398424</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>370041</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>760325</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>198</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>142249</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>120606</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>262855</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>132050</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>112074</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>251275</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>149514</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>127770</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>273751</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>784</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>768</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>573722</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>519245</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1092967</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>554146</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>503550</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1068520</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>590560</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>532952</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>1115550</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>